--- a/research/traditional_assets/database/data/sweden/sweden_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0334</v>
+        <v>0.045</v>
       </c>
       <c r="E2">
-        <v>0.09449999999999999</v>
+        <v>0.06985</v>
       </c>
       <c r="F2">
-        <v>0.1215</v>
+        <v>0.0718</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>7363.5</v>
+        <v>6075.1</v>
       </c>
       <c r="L2">
-        <v>0.4374313125612618</v>
+        <v>0.4385530514127313</v>
       </c>
       <c r="M2">
-        <v>3900.9657</v>
+        <v>4503.3</v>
       </c>
       <c r="N2">
-        <v>0.05160314701271902</v>
+        <v>0.06996004325022993</v>
       </c>
       <c r="O2">
-        <v>0.5297705846404563</v>
+        <v>0.7412717486131916</v>
       </c>
       <c r="P2">
-        <v>3889.5657</v>
+        <v>4334.4</v>
       </c>
       <c r="Q2">
-        <v>0.05145234438557851</v>
+        <v>0.06733613382714822</v>
       </c>
       <c r="R2">
-        <v>0.5282224078223671</v>
+        <v>0.7134697371236687</v>
       </c>
       <c r="S2">
-        <v>11.4</v>
+        <v>168.9</v>
       </c>
       <c r="T2">
-        <v>0.00292235330343971</v>
+        <v>0.03750582905869029</v>
       </c>
       <c r="U2">
-        <v>212542.4</v>
+        <v>92541.39999999999</v>
       </c>
       <c r="V2">
-        <v>2.811574763048065</v>
+        <v>1.437656906365738</v>
       </c>
       <c r="W2">
-        <v>0.1397227675649949</v>
+        <v>0.1005610219585733</v>
       </c>
       <c r="X2">
-        <v>0.1066812979307425</v>
+        <v>0.1691932043136594</v>
       </c>
       <c r="Y2">
-        <v>0.03304146963425239</v>
+        <v>-0.06863218235508613</v>
       </c>
       <c r="Z2">
-        <v>0.05319705667497207</v>
+        <v>0.04087630613646228</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03889920222617293</v>
+        <v>0.06199929306763789</v>
       </c>
       <c r="AC2">
-        <v>-0.03889920222617293</v>
+        <v>-0.06199929306763789</v>
       </c>
       <c r="AD2">
-        <v>424378.7</v>
+        <v>364292.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>424378.7</v>
+        <v>364292.1</v>
       </c>
       <c r="AG2">
-        <v>211836.3</v>
+        <v>271750.7000000001</v>
       </c>
       <c r="AH2">
-        <v>0.8488011981418241</v>
+        <v>0.8498358962323903</v>
       </c>
       <c r="AI2">
-        <v>0.8719865998274432</v>
+        <v>0.8772447223904535</v>
       </c>
       <c r="AJ2">
-        <v>0.7369967414878937</v>
+        <v>0.8084923760927264</v>
       </c>
       <c r="AK2">
-        <v>0.7727362761588237</v>
+        <v>0.8420448732071152</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0275</v>
+        <v>0.0373</v>
       </c>
       <c r="E3">
-        <v>0.0154</v>
+        <v>0.0565</v>
       </c>
       <c r="F3">
-        <v>0.066</v>
+        <v>0.0924</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2134.5</v>
+        <v>1870.4</v>
       </c>
       <c r="L3">
-        <v>0.4056134083307997</v>
+        <v>0.4407266900728105</v>
       </c>
       <c r="M3">
-        <v>928</v>
+        <v>1661.2</v>
       </c>
       <c r="N3">
-        <v>0.04324344475044152</v>
+        <v>0.08297122079375069</v>
       </c>
       <c r="O3">
-        <v>0.4347622394003279</v>
+        <v>0.8881522668947819</v>
       </c>
       <c r="P3">
-        <v>928</v>
+        <v>1661.2</v>
       </c>
       <c r="Q3">
-        <v>0.04324344475044152</v>
+        <v>0.08297122079375069</v>
       </c>
       <c r="R3">
-        <v>0.4347622394003279</v>
+        <v>0.8881522668947819</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>70168.7</v>
+        <v>51070.5</v>
       </c>
       <c r="V3">
-        <v>3.26975894575464</v>
+        <v>2.550795648655938</v>
       </c>
       <c r="W3">
-        <v>0.1141553732444834</v>
+        <v>0.08977029478675715</v>
       </c>
       <c r="X3">
-        <v>0.1958797228162847</v>
+        <v>0.2198015564868333</v>
       </c>
       <c r="Y3">
-        <v>-0.08172434957180123</v>
+        <v>-0.1300312617000762</v>
       </c>
       <c r="Z3">
-        <v>0.04059162697417899</v>
+        <v>0.032761081635221</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03799410469785218</v>
+        <v>0.06049001369141159</v>
       </c>
       <c r="AC3">
-        <v>-0.03799410469785218</v>
+        <v>-0.06049001369141159</v>
       </c>
       <c r="AD3">
-        <v>179662.9</v>
+        <v>148873.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>179662.9</v>
+        <v>148873.2</v>
       </c>
       <c r="AG3">
-        <v>109494.2</v>
+        <v>97802.70000000001</v>
       </c>
       <c r="AH3">
-        <v>0.8932995165142888</v>
+        <v>0.8814562454927511</v>
       </c>
       <c r="AI3">
-        <v>0.8960756549760424</v>
+        <v>0.8959478294780781</v>
       </c>
       <c r="AJ3">
-        <v>0.836126551211455</v>
+        <v>0.8300738134218721</v>
       </c>
       <c r="AK3">
-        <v>0.8401239919896264</v>
+        <v>0.8497762230835598</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TF Bank AB (publ) (OM:TFBANK)</t>
+          <t>Swedbank AB (publ) (OM:SWED A)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.189</v>
+        <v>0.0359</v>
       </c>
       <c r="E4">
-        <v>0.213</v>
+        <v>0.0119</v>
       </c>
       <c r="F4">
-        <v>0.34</v>
+        <v>0.0718</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>29.5</v>
+        <v>1791.9</v>
       </c>
       <c r="L4">
-        <v>0.3482880755608028</v>
+        <v>0.4187954285180078</v>
       </c>
       <c r="M4">
-        <v>14.63</v>
+        <v>1874.6</v>
       </c>
       <c r="N4">
-        <v>0.02681943171402383</v>
+        <v>0.09813632080410428</v>
       </c>
       <c r="O4">
-        <v>0.4959322033898305</v>
+        <v>1.046152129025057</v>
       </c>
       <c r="P4">
-        <v>3.23</v>
+        <v>1874.6</v>
       </c>
       <c r="Q4">
-        <v>0.005921173235563703</v>
+        <v>0.09813632080410428</v>
       </c>
       <c r="R4">
-        <v>0.1094915254237288</v>
+        <v>1.046152129025057</v>
       </c>
       <c r="S4">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.7792207792207793</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>295.7</v>
+        <v>40934.9</v>
       </c>
       <c r="V4">
-        <v>0.5420714940421631</v>
+        <v>2.142964087530101</v>
       </c>
       <c r="W4">
-        <v>0.2574171029668412</v>
+        <v>0.09522873177160836</v>
       </c>
       <c r="X4">
-        <v>0.03951702465955135</v>
+        <v>0.1809719381989873</v>
       </c>
       <c r="Y4">
-        <v>0.2179000783072899</v>
+        <v>-0.08574320642737894</v>
       </c>
       <c r="Z4">
-        <v>-0.6208767042955577</v>
+        <v>0.05493739343016209</v>
       </c>
       <c r="AA4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03868239559310931</v>
+        <v>0.06194185546329295</v>
       </c>
       <c r="AC4">
-        <v>-0.03868239559310931</v>
+        <v>-0.06194185546329295</v>
       </c>
       <c r="AD4">
-        <v>22.6</v>
+        <v>106405.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>22.6</v>
+        <v>106405.1</v>
       </c>
       <c r="AG4">
-        <v>-273.1</v>
+        <v>65470.2</v>
       </c>
       <c r="AH4">
-        <v>0.03978172856891393</v>
+        <v>0.8478014391217709</v>
       </c>
       <c r="AI4">
-        <v>0.1359807460890494</v>
+        <v>0.8747167993476109</v>
       </c>
       <c r="AJ4">
-        <v>-1.002569750367107</v>
+        <v>0.774133817022615</v>
       </c>
       <c r="AK4">
-        <v>2.108880308880309</v>
+        <v>0.8111752775048539</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.04849999999999999</v>
+        <v>0.0527</v>
       </c>
       <c r="E5">
-        <v>0.173</v>
+        <v>0.0832</v>
       </c>
       <c r="F5">
-        <v>0.143</v>
+        <v>0.0704</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2783.2</v>
+        <v>2319</v>
       </c>
       <c r="L5">
-        <v>0.461474689525957</v>
+        <v>0.4512638891591586</v>
       </c>
       <c r="M5">
-        <v>2029.6357</v>
+        <v>967.5</v>
       </c>
       <c r="N5">
-        <v>0.06731436142692263</v>
+        <v>0.03950333992062585</v>
       </c>
       <c r="O5">
-        <v>0.7292453650474274</v>
+        <v>0.4172056921086675</v>
       </c>
       <c r="P5">
-        <v>2029.6357</v>
+        <v>798.6</v>
       </c>
       <c r="Q5">
-        <v>0.06731436142692263</v>
+        <v>0.03260709794378481</v>
       </c>
       <c r="R5">
-        <v>0.7292453650474274</v>
+        <v>0.344372574385511</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>168.9</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.1745736434108527</v>
       </c>
       <c r="U5">
-        <v>67185.7</v>
+        <v>237.5</v>
       </c>
       <c r="V5">
-        <v>2.228263176746839</v>
+        <v>0.009697202306096785</v>
       </c>
       <c r="W5">
-        <v>0.1505213516203003</v>
+        <v>0.1058933121455382</v>
       </c>
       <c r="X5">
-        <v>0.1066812979307425</v>
+        <v>0.1574144704283315</v>
       </c>
       <c r="Y5">
-        <v>0.04384005368955771</v>
+        <v>-0.05152115828279329</v>
       </c>
       <c r="Z5">
-        <v>0.06422903538768411</v>
+        <v>0.03928348104739641</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03889920222617293</v>
+        <v>0.06205673067198284</v>
       </c>
       <c r="AC5">
-        <v>-0.03889920222617293</v>
+        <v>-0.06205673067198284</v>
       </c>
       <c r="AD5">
-        <v>109141.8</v>
+        <v>108710.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>109141.8</v>
+        <v>108710.5</v>
       </c>
       <c r="AG5">
-        <v>41956.10000000001</v>
+        <v>108473</v>
       </c>
       <c r="AH5">
-        <v>0.783538918570442</v>
+        <v>0.8161320279485083</v>
       </c>
       <c r="AI5">
-        <v>0.832881567018617</v>
+        <v>0.8590279303298443</v>
       </c>
       <c r="AJ5">
-        <v>0.5818532556162518</v>
+        <v>0.815803604869266</v>
       </c>
       <c r="AK5">
-        <v>0.6570475526775298</v>
+        <v>0.8587628678260607</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swedbank AB (publ) (OM:SWED A)</t>
+          <t>Collector Bank AB (OM:COLL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,13 +1088,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0334</v>
+        <v>0.118</v>
       </c>
       <c r="E6">
-        <v>0.0135</v>
-      </c>
-      <c r="F6">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,209 +1106,87 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>2348.6</v>
+        <v>93.8</v>
       </c>
       <c r="L6">
-        <v>0.4452491089709562</v>
+        <v>0.4908424908424908</v>
       </c>
       <c r="M6">
-        <v>928.7</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.04113624081997856</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.3954270629311079</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>928.7</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.04113624081997856</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.3954270629311079</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>74515.2</v>
+        <v>298.5</v>
       </c>
       <c r="V6">
-        <v>3.30060860552263</v>
+        <v>0.3955738139411609</v>
       </c>
       <c r="W6">
-        <v>0.1397227675649949</v>
+        <v>0.1579656449983159</v>
       </c>
       <c r="X6">
-        <v>0.1510750714636359</v>
+        <v>0.07338393413047858</v>
       </c>
       <c r="Y6">
-        <v>-0.01135230389864098</v>
+        <v>0.08458171086783736</v>
       </c>
       <c r="Z6">
-        <v>0.0569103673582123</v>
+        <v>0.2936385986478182</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.03891415103503149</v>
+        <v>0.06572997868877885</v>
       </c>
       <c r="AC6">
-        <v>-0.03891415103503149</v>
+        <v>-0.06572997868877885</v>
       </c>
       <c r="AD6">
-        <v>135117.5</v>
+        <v>303.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>135117.5</v>
+        <v>303.3</v>
       </c>
       <c r="AG6">
-        <v>60602.3</v>
+        <v>4.800000000000011</v>
       </c>
       <c r="AH6">
-        <v>0.8568351176996925</v>
+        <v>0.286700066168825</v>
       </c>
       <c r="AI6">
-        <v>0.8777437307267311</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AJ6">
-        <v>0.728581304062949</v>
+        <v>0.006320779562812761</v>
       </c>
       <c r="AK6">
-        <v>0.7630407657314525</v>
+        <v>0.007850834151128574</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Collector AB (publ) (OM:COLL)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0229</v>
-      </c>
-      <c r="E7">
-        <v>0.09449999999999999</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>67.7</v>
-      </c>
-      <c r="L7">
-        <v>0.3750692520775624</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>-0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>377.1</v>
-      </c>
-      <c r="V7">
-        <v>0.4373187985619854</v>
-      </c>
-      <c r="W7">
-        <v>0.1299673641773853</v>
-      </c>
-      <c r="X7">
-        <v>0.04818409956409734</v>
-      </c>
-      <c r="Y7">
-        <v>0.08178326461328797</v>
-      </c>
-      <c r="Z7">
-        <v>0.5237957051654093</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.03948710780780827</v>
-      </c>
-      <c r="AC7">
-        <v>-0.03948710780780827</v>
-      </c>
-      <c r="AD7">
-        <v>433.9</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>433.9</v>
-      </c>
-      <c r="AG7">
-        <v>56.79999999999995</v>
-      </c>
-      <c r="AH7">
-        <v>0.3347477241166487</v>
-      </c>
-      <c r="AI7">
-        <v>0.4188628245969688</v>
-      </c>
-      <c r="AJ7">
-        <v>0.06179958655206175</v>
-      </c>
-      <c r="AK7">
-        <v>0.08621736490588944</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/sweden/sweden_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.045</v>
+        <v>0.10585</v>
       </c>
       <c r="E2">
-        <v>0.06985</v>
+        <v>0.1075</v>
       </c>
       <c r="F2">
-        <v>0.0718</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>6075.1</v>
+        <v>9114.200000000001</v>
       </c>
       <c r="L2">
-        <v>0.4385530514127313</v>
+        <v>0.4730594555316223</v>
       </c>
       <c r="M2">
-        <v>4503.3</v>
+        <v>4316.7</v>
       </c>
       <c r="N2">
-        <v>0.06996004325022993</v>
+        <v>0.05848727335792037</v>
       </c>
       <c r="O2">
-        <v>0.7412717486131916</v>
+        <v>0.4736235763972702</v>
       </c>
       <c r="P2">
-        <v>4334.4</v>
+        <v>3641.9</v>
       </c>
       <c r="Q2">
-        <v>0.06733613382714822</v>
+        <v>0.04934436047031534</v>
       </c>
       <c r="R2">
-        <v>0.7134697371236687</v>
+        <v>0.3995852625573281</v>
       </c>
       <c r="S2">
-        <v>168.9</v>
+        <v>674.8000000000001</v>
       </c>
       <c r="T2">
-        <v>0.03750582905869029</v>
+        <v>0.1563231171960062</v>
       </c>
       <c r="U2">
-        <v>92541.39999999999</v>
+        <v>71117.39999999999</v>
       </c>
       <c r="V2">
-        <v>1.437656906365738</v>
+        <v>0.9635746784128075</v>
       </c>
       <c r="W2">
-        <v>0.1005610219585733</v>
+        <v>0.1952215740696986</v>
       </c>
       <c r="X2">
-        <v>0.1691932043136594</v>
+        <v>0.1190516355183954</v>
       </c>
       <c r="Y2">
-        <v>-0.06863218235508613</v>
+        <v>0.07616993855130327</v>
       </c>
       <c r="Z2">
-        <v>0.04087630613646228</v>
+        <v>0.0600040238340536</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06199929306763789</v>
+        <v>0.05334014995983824</v>
       </c>
       <c r="AC2">
-        <v>-0.06199929306763789</v>
+        <v>-0.05334014995983824</v>
       </c>
       <c r="AD2">
-        <v>364292.1</v>
+        <v>381516.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>364292.1</v>
+        <v>381516.1</v>
       </c>
       <c r="AG2">
-        <v>271750.7000000001</v>
+        <v>310398.7</v>
       </c>
       <c r="AH2">
-        <v>0.8498358962323903</v>
+        <v>0.8379041289250528</v>
       </c>
       <c r="AI2">
-        <v>0.8772447223904535</v>
+        <v>0.8697936270869892</v>
       </c>
       <c r="AJ2">
-        <v>0.8084923760927264</v>
+        <v>0.8078996992487074</v>
       </c>
       <c r="AK2">
-        <v>0.8420448732071152</v>
+        <v>0.8445972622852819</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0373</v>
+        <v>0.0733</v>
       </c>
       <c r="E3">
-        <v>0.0565</v>
+        <v>0.101</v>
       </c>
       <c r="F3">
-        <v>0.0924</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1870.4</v>
+        <v>2536.9</v>
       </c>
       <c r="L3">
-        <v>0.4407266900728105</v>
+        <v>0.4603756464930587</v>
       </c>
       <c r="M3">
-        <v>1661.2</v>
+        <v>1453.5</v>
       </c>
       <c r="N3">
-        <v>0.08297122079375069</v>
+        <v>0.06741588668008645</v>
       </c>
       <c r="O3">
-        <v>0.8881522668947819</v>
+        <v>0.5729433560644881</v>
       </c>
       <c r="P3">
-        <v>1661.2</v>
+        <v>1453.5</v>
       </c>
       <c r="Q3">
-        <v>0.08297122079375069</v>
+        <v>0.06741588668008645</v>
       </c>
       <c r="R3">
-        <v>0.8881522668947819</v>
+        <v>0.5729433560644881</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>51070.5</v>
+        <v>44257.7</v>
       </c>
       <c r="V3">
-        <v>2.550795648655938</v>
+        <v>2.052749974490032</v>
       </c>
       <c r="W3">
-        <v>0.08977029478675715</v>
+        <v>0.1467400106429745</v>
       </c>
       <c r="X3">
-        <v>0.2198015564868333</v>
+        <v>0.1643863632388378</v>
       </c>
       <c r="Y3">
-        <v>-0.1300312617000762</v>
+        <v>-0.01764635259586328</v>
       </c>
       <c r="Z3">
-        <v>0.032761081635221</v>
+        <v>0.04804359975204428</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06049001369141159</v>
+        <v>0.05198456050712442</v>
       </c>
       <c r="AC3">
-        <v>-0.06049001369141159</v>
+        <v>-0.05198456050712442</v>
       </c>
       <c r="AD3">
-        <v>148873.2</v>
+        <v>161176</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>148873.2</v>
+        <v>161176</v>
       </c>
       <c r="AG3">
-        <v>97802.70000000001</v>
+        <v>116918.3</v>
       </c>
       <c r="AH3">
-        <v>0.8814562454927511</v>
+        <v>0.8820146199822476</v>
       </c>
       <c r="AI3">
-        <v>0.8959478294780781</v>
+        <v>0.8960569292137486</v>
       </c>
       <c r="AJ3">
-        <v>0.8300738134218721</v>
+        <v>0.8443065168961247</v>
       </c>
       <c r="AK3">
-        <v>0.8497762230835598</v>
+        <v>0.8621352536743778</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0359</v>
+        <v>0.09570000000000001</v>
       </c>
       <c r="E4">
-        <v>0.0119</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="F4">
-        <v>0.0718</v>
+        <v>0.123</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1791.9</v>
+        <v>3038</v>
       </c>
       <c r="L4">
-        <v>0.4187954285180078</v>
+        <v>0.4785910079082517</v>
       </c>
       <c r="M4">
-        <v>1874.6</v>
+        <v>1006.1</v>
       </c>
       <c r="N4">
-        <v>0.09813632080410428</v>
+        <v>0.0443739745602738</v>
       </c>
       <c r="O4">
-        <v>1.046152129025057</v>
+        <v>0.331171823568137</v>
       </c>
       <c r="P4">
-        <v>1874.6</v>
+        <v>1006.1</v>
       </c>
       <c r="Q4">
-        <v>0.09813632080410428</v>
+        <v>0.0443739745602738</v>
       </c>
       <c r="R4">
-        <v>1.046152129025057</v>
+        <v>0.331171823568137</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>40934.9</v>
+        <v>26427.5</v>
       </c>
       <c r="V4">
-        <v>2.142964087530101</v>
+        <v>1.165583155443431</v>
       </c>
       <c r="W4">
-        <v>0.09522873177160836</v>
+        <v>0.1993778466142518</v>
       </c>
       <c r="X4">
-        <v>0.1809719381989873</v>
+        <v>0.1234524964769196</v>
       </c>
       <c r="Y4">
-        <v>-0.08574320642737894</v>
+        <v>0.07592535013733218</v>
       </c>
       <c r="Z4">
-        <v>0.05493739343016209</v>
+        <v>0.07988231207937141</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06194185546329295</v>
+        <v>0.0532924923929919</v>
       </c>
       <c r="AC4">
-        <v>-0.06194185546329295</v>
+        <v>-0.0532924923929919</v>
       </c>
       <c r="AD4">
-        <v>106405.1</v>
+        <v>104942.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>106405.1</v>
+        <v>104942.9</v>
       </c>
       <c r="AG4">
-        <v>65470.2</v>
+        <v>78515.39999999999</v>
       </c>
       <c r="AH4">
-        <v>0.8478014391217709</v>
+        <v>0.822332762088796</v>
       </c>
       <c r="AI4">
-        <v>0.8747167993476109</v>
+        <v>0.8556234447716607</v>
       </c>
       <c r="AJ4">
-        <v>0.774133817022615</v>
+        <v>0.7759312807964533</v>
       </c>
       <c r="AK4">
-        <v>0.8111752775048539</v>
+        <v>0.815970767994862</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0527</v>
+        <v>0.116</v>
       </c>
       <c r="E5">
-        <v>0.0832</v>
+        <v>0.114</v>
       </c>
       <c r="F5">
-        <v>0.0704</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2319</v>
+        <v>3418.7</v>
       </c>
       <c r="L5">
-        <v>0.4512638891591586</v>
+        <v>0.4766598812079975</v>
       </c>
       <c r="M5">
-        <v>967.5</v>
+        <v>1856</v>
       </c>
       <c r="N5">
-        <v>0.03950333992062585</v>
+        <v>0.06469243210083096</v>
       </c>
       <c r="O5">
-        <v>0.4172056921086675</v>
+        <v>0.5428964226167842</v>
       </c>
       <c r="P5">
-        <v>798.6</v>
+        <v>1182.3</v>
       </c>
       <c r="Q5">
-        <v>0.03260709794378481</v>
+        <v>0.04121005521164464</v>
       </c>
       <c r="R5">
-        <v>0.344372574385511</v>
+        <v>0.3458332114546465</v>
       </c>
       <c r="S5">
-        <v>168.9</v>
+        <v>673.7</v>
       </c>
       <c r="T5">
-        <v>0.1745736434108527</v>
+        <v>0.3629849137931035</v>
       </c>
       <c r="U5">
-        <v>237.5</v>
+        <v>231</v>
       </c>
       <c r="V5">
-        <v>0.009697202306096785</v>
+        <v>0.008051698176342647</v>
       </c>
       <c r="W5">
-        <v>0.1058933121455382</v>
+        <v>0.1916300917595753</v>
       </c>
       <c r="X5">
-        <v>0.1574144704283315</v>
+        <v>0.1146507745598711</v>
       </c>
       <c r="Y5">
-        <v>-0.05152115828279329</v>
+        <v>0.0769793171997042</v>
       </c>
       <c r="Z5">
-        <v>0.03928348104739641</v>
+        <v>0.05678112563146657</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06205673067198284</v>
+        <v>0.05338780752668458</v>
       </c>
       <c r="AC5">
-        <v>-0.06205673067198284</v>
+        <v>-0.05338780752668458</v>
       </c>
       <c r="AD5">
-        <v>108710.5</v>
+        <v>115226.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>108710.5</v>
+        <v>115226.1</v>
       </c>
       <c r="AG5">
-        <v>108473</v>
+        <v>114995.1</v>
       </c>
       <c r="AH5">
-        <v>0.8161320279485083</v>
+        <v>0.8006499638329939</v>
       </c>
       <c r="AI5">
-        <v>0.8590279303298443</v>
+        <v>0.8522615317706161</v>
       </c>
       <c r="AJ5">
-        <v>0.815803604869266</v>
+        <v>0.8003294714050974</v>
       </c>
       <c r="AK5">
-        <v>0.8587628678260607</v>
+        <v>0.8520086775224607</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Collector Bank AB (OM:COLL)</t>
+          <t>Norion Bank AB (OM:NORION)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.118</v>
+        <v>0.128</v>
       </c>
       <c r="E6">
-        <v>0.19</v>
+        <v>0.207</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1106,19 +1106,19 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>93.8</v>
+        <v>120.6</v>
       </c>
       <c r="L6">
-        <v>0.4908424908424908</v>
+        <v>0.5110169491525424</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.001246035342093339</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.009121061359867332</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1130,58 +1130,61 @@
         <v>-0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>298.5</v>
+        <v>201.2</v>
       </c>
       <c r="V6">
-        <v>0.3955738139411609</v>
+        <v>0.2279111916628908</v>
       </c>
       <c r="W6">
-        <v>0.1579656449983159</v>
+        <v>0.1988130563798219</v>
       </c>
       <c r="X6">
-        <v>0.07338393413047858</v>
+        <v>0.05969390404631112</v>
       </c>
       <c r="Y6">
-        <v>0.08458171086783736</v>
+        <v>0.1391191523335108</v>
       </c>
       <c r="Z6">
-        <v>0.2936385986478182</v>
+        <v>0.3859993457638207</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06572997868877885</v>
+        <v>0.05655812045647923</v>
       </c>
       <c r="AC6">
-        <v>-0.06572997868877885</v>
+        <v>-0.05655812045647923</v>
       </c>
       <c r="AD6">
-        <v>303.3</v>
+        <v>171.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>303.3</v>
+        <v>171.1</v>
       </c>
       <c r="AG6">
-        <v>4.800000000000011</v>
+        <v>-30.09999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.286700066168825</v>
+        <v>0.1623493690103426</v>
       </c>
       <c r="AI6">
-        <v>0.3333333333333333</v>
+        <v>0.1891443732036259</v>
       </c>
       <c r="AJ6">
-        <v>0.006320779562812761</v>
+        <v>-0.03529963644892693</v>
       </c>
       <c r="AK6">
-        <v>0.007850834151128574</v>
+        <v>-0.04279215240261586</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/research/traditional_assets/database/data/sweden/sweden_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.10585</v>
+        <v>0.11</v>
       </c>
       <c r="E2">
-        <v>0.1075</v>
+        <v>0.118</v>
       </c>
       <c r="F2">
-        <v>0.07829999999999999</v>
+        <v>-0.0588</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>9114.200000000001</v>
+        <v>9792</v>
       </c>
       <c r="L2">
-        <v>0.4730594555316223</v>
+        <v>0.4568527918781726</v>
       </c>
       <c r="M2">
-        <v>4316.7</v>
+        <v>6231.9</v>
       </c>
       <c r="N2">
-        <v>0.05848727335792037</v>
+        <v>0.08825291266191879</v>
       </c>
       <c r="O2">
-        <v>0.4736235763972702</v>
+        <v>0.6364276960784313</v>
       </c>
       <c r="P2">
-        <v>3641.9</v>
+        <v>5618.4</v>
       </c>
       <c r="Q2">
-        <v>0.04934436047031534</v>
+        <v>0.07956484611430294</v>
       </c>
       <c r="R2">
-        <v>0.3995852625573281</v>
+        <v>0.5737745098039215</v>
       </c>
       <c r="S2">
-        <v>674.8000000000001</v>
+        <v>613.5</v>
       </c>
       <c r="T2">
-        <v>0.1563231171960062</v>
+        <v>0.09844509700091465</v>
       </c>
       <c r="U2">
-        <v>71117.39999999999</v>
+        <v>142220.7</v>
       </c>
       <c r="V2">
-        <v>0.9635746784128075</v>
+        <v>2.014055266582736</v>
       </c>
       <c r="W2">
-        <v>0.1952215740696986</v>
+        <v>0.1813880836875385</v>
       </c>
       <c r="X2">
-        <v>0.1190516355183954</v>
+        <v>0.1315811740947988</v>
       </c>
       <c r="Y2">
-        <v>0.07616993855130327</v>
+        <v>0.04980690959273967</v>
       </c>
       <c r="Z2">
-        <v>0.0600040238340536</v>
+        <v>0.0584975611460212</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05334014995983824</v>
+        <v>0.05714609469936387</v>
       </c>
       <c r="AC2">
-        <v>-0.05334014995983824</v>
+        <v>-0.05714609469936387</v>
       </c>
       <c r="AD2">
-        <v>381516.1</v>
+        <v>401693.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>381516.1</v>
+        <v>401693.2</v>
       </c>
       <c r="AG2">
-        <v>310398.7</v>
+        <v>259472.5</v>
       </c>
       <c r="AH2">
-        <v>0.8379041289250528</v>
+        <v>0.850491195033403</v>
       </c>
       <c r="AI2">
-        <v>0.8697936270869892</v>
+        <v>0.8652433384612668</v>
       </c>
       <c r="AJ2">
-        <v>0.8078996992487074</v>
+        <v>0.7860740181516003</v>
       </c>
       <c r="AK2">
-        <v>0.8445972622852819</v>
+        <v>0.8057303904961558</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0733</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="E3">
-        <v>0.101</v>
+        <v>0.11</v>
       </c>
       <c r="F3">
-        <v>0.06059999999999999</v>
+        <v>-0.092</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2536.9</v>
+        <v>2745.5</v>
       </c>
       <c r="L3">
-        <v>0.4603756464930587</v>
+        <v>0.4454594129768144</v>
       </c>
       <c r="M3">
-        <v>1453.5</v>
+        <v>2537.9</v>
       </c>
       <c r="N3">
-        <v>0.06741588668008645</v>
+        <v>0.1235522927204483</v>
       </c>
       <c r="O3">
-        <v>0.5729433560644881</v>
+        <v>0.9243853578583137</v>
       </c>
       <c r="P3">
-        <v>1453.5</v>
+        <v>2537.9</v>
       </c>
       <c r="Q3">
-        <v>0.06741588668008645</v>
+        <v>0.1235522927204483</v>
       </c>
       <c r="R3">
-        <v>0.5729433560644881</v>
+        <v>0.9243853578583137</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>44257.7</v>
+        <v>59240.8</v>
       </c>
       <c r="V3">
-        <v>2.052749974490032</v>
+        <v>2.884013027539908</v>
       </c>
       <c r="W3">
-        <v>0.1467400106429745</v>
+        <v>0.1468472371538754</v>
       </c>
       <c r="X3">
-        <v>0.1643863632388378</v>
+        <v>0.1793527600631629</v>
       </c>
       <c r="Y3">
-        <v>-0.01764635259586328</v>
+        <v>-0.03250552290928752</v>
       </c>
       <c r="Z3">
-        <v>0.04804359975204428</v>
+        <v>0.04558256010200294</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05198456050712442</v>
+        <v>0.05623488617109527</v>
       </c>
       <c r="AC3">
-        <v>-0.05198456050712442</v>
+        <v>-0.05623488617109527</v>
       </c>
       <c r="AD3">
-        <v>161176</v>
+        <v>176707.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>161176</v>
+        <v>176707.1</v>
       </c>
       <c r="AG3">
-        <v>116918.3</v>
+        <v>117466.3</v>
       </c>
       <c r="AH3">
-        <v>0.8820146199822476</v>
+        <v>0.8958616605880307</v>
       </c>
       <c r="AI3">
-        <v>0.8960569292137486</v>
+        <v>0.8991268084214319</v>
       </c>
       <c r="AJ3">
-        <v>0.8443065168961247</v>
+        <v>0.8511594305812588</v>
       </c>
       <c r="AK3">
-        <v>0.8621352536743778</v>
+        <v>0.85560025376736</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09570000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E4">
-        <v>0.09210000000000002</v>
+        <v>0.118</v>
       </c>
       <c r="F4">
-        <v>0.123</v>
+        <v>-0.0588</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>3038</v>
+        <v>3423.4</v>
       </c>
       <c r="L4">
-        <v>0.4785910079082517</v>
+        <v>0.4691388477772296</v>
       </c>
       <c r="M4">
-        <v>1006.1</v>
+        <v>1680.9</v>
       </c>
       <c r="N4">
-        <v>0.0443739745602738</v>
+        <v>0.07572781416973771</v>
       </c>
       <c r="O4">
-        <v>0.331171823568137</v>
+        <v>0.491003096336975</v>
       </c>
       <c r="P4">
-        <v>1006.1</v>
+        <v>1680.9</v>
       </c>
       <c r="Q4">
-        <v>0.0443739745602738</v>
+        <v>0.07572781416973771</v>
       </c>
       <c r="R4">
-        <v>0.331171823568137</v>
+        <v>0.491003096336975</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>26427.5</v>
+        <v>27741.7</v>
       </c>
       <c r="V4">
-        <v>1.165583155443431</v>
+        <v>1.249817539623186</v>
       </c>
       <c r="W4">
-        <v>0.1993778466142518</v>
+        <v>0.1933578085286642</v>
       </c>
       <c r="X4">
-        <v>0.1234524964769196</v>
+        <v>0.1315811740947988</v>
       </c>
       <c r="Y4">
-        <v>0.07592535013733218</v>
+        <v>0.06177663443386541</v>
       </c>
       <c r="Z4">
-        <v>0.07988231207937141</v>
+        <v>0.07583838770156849</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0532924923929919</v>
+        <v>0.05714609469936387</v>
       </c>
       <c r="AC4">
-        <v>-0.0532924923929919</v>
+        <v>-0.05714609469936387</v>
       </c>
       <c r="AD4">
-        <v>104942.9</v>
+        <v>112647.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>104942.9</v>
+        <v>112647.1</v>
       </c>
       <c r="AG4">
-        <v>78515.39999999999</v>
+        <v>84905.40000000001</v>
       </c>
       <c r="AH4">
-        <v>0.822332762088796</v>
+        <v>0.8353901591249721</v>
       </c>
       <c r="AI4">
-        <v>0.8556234447716607</v>
+        <v>0.8454469651312634</v>
       </c>
       <c r="AJ4">
-        <v>0.7759312807964533</v>
+        <v>0.7927527030307558</v>
       </c>
       <c r="AK4">
-        <v>0.815970767994862</v>
+        <v>0.8048057783085936</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.116</v>
+        <v>0.119</v>
       </c>
       <c r="E5">
-        <v>0.114</v>
+        <v>0.142</v>
       </c>
       <c r="F5">
-        <v>0.07829999999999999</v>
+        <v>-0.0333</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,212 +984,90 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>3418.7</v>
+        <v>3623.1</v>
       </c>
       <c r="L5">
-        <v>0.4766598812079975</v>
+        <v>0.454415472024683</v>
       </c>
       <c r="M5">
-        <v>1856</v>
+        <v>2013.1</v>
       </c>
       <c r="N5">
-        <v>0.06469243210083096</v>
+        <v>0.07221520712861057</v>
       </c>
       <c r="O5">
-        <v>0.5428964226167842</v>
+        <v>0.5556291573514394</v>
       </c>
       <c r="P5">
-        <v>1182.3</v>
+        <v>1399.6</v>
       </c>
       <c r="Q5">
-        <v>0.04121005521164464</v>
+        <v>0.05020734384640771</v>
       </c>
       <c r="R5">
-        <v>0.3458332114546465</v>
+        <v>0.386299025696227</v>
       </c>
       <c r="S5">
-        <v>673.7</v>
+        <v>613.5</v>
       </c>
       <c r="T5">
-        <v>0.3629849137931035</v>
+        <v>0.3047538622025732</v>
       </c>
       <c r="U5">
-        <v>231</v>
+        <v>55238.2</v>
       </c>
       <c r="V5">
-        <v>0.008051698176342647</v>
+        <v>1.981539940594912</v>
       </c>
       <c r="W5">
-        <v>0.1916300917595753</v>
+        <v>0.1813880836875385</v>
       </c>
       <c r="X5">
-        <v>0.1146507745598711</v>
+        <v>0.1174286898885463</v>
       </c>
       <c r="Y5">
-        <v>0.0769793171997042</v>
+        <v>0.06395939379899215</v>
       </c>
       <c r="Z5">
-        <v>0.05678112563146657</v>
+        <v>0.05907338996839284</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05338780752668458</v>
+        <v>0.05737984209872149</v>
       </c>
       <c r="AC5">
-        <v>-0.05338780752668458</v>
+        <v>-0.05737984209872149</v>
       </c>
       <c r="AD5">
-        <v>115226.1</v>
+        <v>112339</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>115226.1</v>
+        <v>112339</v>
       </c>
       <c r="AG5">
-        <v>114995.1</v>
+        <v>57100.8</v>
       </c>
       <c r="AH5">
-        <v>0.8006499638329939</v>
+        <v>0.8011887424633813</v>
       </c>
       <c r="AI5">
-        <v>0.8522615317706161</v>
+        <v>0.8353397827234669</v>
       </c>
       <c r="AJ5">
-        <v>0.8003294714050974</v>
+        <v>0.6719543595223189</v>
       </c>
       <c r="AK5">
-        <v>0.8520086775224607</v>
+        <v>0.7205621062833145</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Norion Bank AB (OM:NORION)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.128</v>
-      </c>
-      <c r="E6">
-        <v>0.207</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>120.6</v>
-      </c>
-      <c r="L6">
-        <v>0.5110169491525424</v>
-      </c>
-      <c r="M6">
-        <v>1.1</v>
-      </c>
-      <c r="N6">
-        <v>0.001246035342093339</v>
-      </c>
-      <c r="O6">
-        <v>0.009121061359867332</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>1.1</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6">
-        <v>201.2</v>
-      </c>
-      <c r="V6">
-        <v>0.2279111916628908</v>
-      </c>
-      <c r="W6">
-        <v>0.1988130563798219</v>
-      </c>
-      <c r="X6">
-        <v>0.05969390404631112</v>
-      </c>
-      <c r="Y6">
-        <v>0.1391191523335108</v>
-      </c>
-      <c r="Z6">
-        <v>0.3859993457638207</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.05655812045647923</v>
-      </c>
-      <c r="AC6">
-        <v>-0.05655812045647923</v>
-      </c>
-      <c r="AD6">
-        <v>171.1</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>171.1</v>
-      </c>
-      <c r="AG6">
-        <v>-30.09999999999999</v>
-      </c>
-      <c r="AH6">
-        <v>0.1623493690103426</v>
-      </c>
-      <c r="AI6">
-        <v>0.1891443732036259</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.03529963644892693</v>
-      </c>
-      <c r="AK6">
-        <v>-0.04279215240261586</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/sweden/sweden_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.11</v>
+        <v>0.1125</v>
       </c>
       <c r="E2">
-        <v>0.118</v>
+        <v>0.13</v>
       </c>
       <c r="F2">
-        <v>-0.0588</v>
+        <v>-0.04605</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>9792</v>
+        <v>9919.200000000001</v>
       </c>
       <c r="L2">
-        <v>0.4568527918781726</v>
+        <v>0.4571839438060868</v>
       </c>
       <c r="M2">
-        <v>6231.9</v>
+        <v>6284.2</v>
       </c>
       <c r="N2">
-        <v>0.08825291266191879</v>
+        <v>0.088150305233863</v>
       </c>
       <c r="O2">
-        <v>0.6364276960784313</v>
+        <v>0.6335389950802484</v>
       </c>
       <c r="P2">
         <v>5618.4</v>
       </c>
       <c r="Q2">
-        <v>0.07956484611430294</v>
+        <v>0.07881093455426877</v>
       </c>
       <c r="R2">
-        <v>0.5737745098039215</v>
+        <v>0.5664166465037502</v>
       </c>
       <c r="S2">
-        <v>613.5</v>
+        <v>665.8</v>
       </c>
       <c r="T2">
-        <v>0.09844509700091465</v>
+        <v>0.1059482511695999</v>
       </c>
       <c r="U2">
-        <v>142220.7</v>
+        <v>142575.4</v>
       </c>
       <c r="V2">
-        <v>2.014055266582736</v>
+        <v>1.999946696292306</v>
       </c>
       <c r="W2">
-        <v>0.1813880836875385</v>
+        <v>0.1774016083059369</v>
       </c>
       <c r="X2">
-        <v>0.1315811740947988</v>
+        <v>0.1244543317180992</v>
       </c>
       <c r="Y2">
-        <v>0.04980690959273967</v>
+        <v>0.05294727658783772</v>
       </c>
       <c r="Z2">
-        <v>0.0584975611460212</v>
+        <v>0.05910107462442625</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05714609469936387</v>
+        <v>0.05725385159341047</v>
       </c>
       <c r="AC2">
-        <v>-0.05714609469936387</v>
+        <v>-0.05725385159341047</v>
       </c>
       <c r="AD2">
-        <v>401693.2</v>
+        <v>401946.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>401693.2</v>
+        <v>401946.1</v>
       </c>
       <c r="AG2">
-        <v>259472.5</v>
+        <v>259370.7</v>
       </c>
       <c r="AH2">
-        <v>0.850491195033403</v>
+        <v>0.8493570962630249</v>
       </c>
       <c r="AI2">
-        <v>0.8652433384612668</v>
+        <v>0.8637124027897783</v>
       </c>
       <c r="AJ2">
-        <v>0.7860740181516003</v>
+        <v>0.7844023004878421</v>
       </c>
       <c r="AK2">
-        <v>0.8057303904961558</v>
+        <v>0.8035154830513123</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>0.1468472371538754</v>
       </c>
       <c r="X3">
-        <v>0.1793527600631629</v>
+        <v>0.1792668975126891</v>
       </c>
       <c r="Y3">
-        <v>-0.03250552290928752</v>
+        <v>-0.03241966035881372</v>
       </c>
       <c r="Z3">
         <v>0.04558256010200294</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05623488617109527</v>
+        <v>0.05622594458767126</v>
       </c>
       <c r="AC3">
-        <v>-0.05623488617109527</v>
+        <v>-0.05622594458767126</v>
       </c>
       <c r="AD3">
         <v>176707.1</v>
@@ -898,10 +898,10 @@
         <v>0.1933578085286642</v>
       </c>
       <c r="X4">
-        <v>0.1315811740947988</v>
+        <v>0.1315260244267056</v>
       </c>
       <c r="Y4">
-        <v>0.06177663443386541</v>
+        <v>0.06183178410195864</v>
       </c>
       <c r="Z4">
         <v>0.07583838770156849</v>
@@ -910,10 +910,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05714609469936387</v>
+        <v>0.05713701652127474</v>
       </c>
       <c r="AC4">
-        <v>-0.05714609469936387</v>
+        <v>-0.05713701652127474</v>
       </c>
       <c r="AD4">
         <v>112647.1</v>
@@ -1023,10 +1023,10 @@
         <v>0.1813880836875385</v>
       </c>
       <c r="X5">
-        <v>0.1174286898885463</v>
+        <v>0.1173826390094928</v>
       </c>
       <c r="Y5">
-        <v>0.06395939379899215</v>
+        <v>0.06400544467804564</v>
       </c>
       <c r="Z5">
         <v>0.05907338996839284</v>
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05737984209872149</v>
+        <v>0.05737068666554619</v>
       </c>
       <c r="AC5">
-        <v>-0.05737984209872149</v>
+        <v>-0.05737068666554619</v>
       </c>
       <c r="AD5">
         <v>112339</v>
@@ -1068,6 +1068,131 @@
         <v>0</v>
       </c>
       <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Norion Bank AB (publ) (OM:NORION)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.115</v>
+      </c>
+      <c r="E6">
+        <v>0.172</v>
+      </c>
+      <c r="F6">
+        <v>0.09</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>127.2</v>
+      </c>
+      <c r="L6">
+        <v>0.4842025123715265</v>
+      </c>
+      <c r="M6">
+        <v>52.3</v>
+      </c>
+      <c r="N6">
+        <v>0.0774241302738712</v>
+      </c>
+      <c r="O6">
+        <v>0.4111635220125786</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>52.3</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>354.7</v>
+      </c>
+      <c r="V6">
+        <v>0.5250925240562546</v>
+      </c>
+      <c r="W6">
+        <v>0.1734151329243354</v>
+      </c>
+      <c r="X6">
+        <v>0.06791130080798352</v>
+      </c>
+      <c r="Y6">
+        <v>0.1055038321163519</v>
+      </c>
+      <c r="Z6">
+        <v>0.3734717088427636</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06137275686750632</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06137275686750632</v>
+      </c>
+      <c r="AD6">
+        <v>252.9</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>252.9</v>
+      </c>
+      <c r="AG6">
+        <v>-101.8</v>
+      </c>
+      <c r="AH6">
+        <v>0.272404136148212</v>
+      </c>
+      <c r="AI6">
+        <v>0.2266738370529712</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.1774446574864912</v>
+      </c>
+      <c r="AK6">
+        <v>-0.1337713534822602</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>0</v>
       </c>
     </row>
